--- a/review/abilities/workbooks/28_Class_Unbalanced.xlsx
+++ b/review/abilities/workbooks/28_Class_Unbalanced.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Level 1'!$A$4:$M$7</definedName>
@@ -27,9 +27,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'All Signatures'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Power Watchlist'!$A$4:$J$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Power Watchlist'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$R$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$Q$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Change Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$R$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -183,7 +183,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -220,19 +220,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="001F3864"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1349,15 +1336,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1683,15 +1667,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2013,15 +1994,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2693,15 +2671,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3265,15 +3240,12 @@
       <formula>H5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>H5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>H5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="H5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3297,7 +3269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3312,12 +3284,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" style="10" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" style="10" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3398,30 +3369,25 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Playtest status</t>
+          <t>Book issue</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Book issue</t>
+          <t>Foundry issue</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Foundry issue</t>
+          <t>Commit SHA</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Commit SHA</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3445,7 +3411,6 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr"/>
@@ -3465,7 +3430,6 @@
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr"/>
@@ -3485,7 +3449,6 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="8" t="inlineStr"/>
@@ -3505,7 +3468,6 @@
       <c r="O8" s="8" t="inlineStr"/>
       <c r="P8" s="8" t="inlineStr"/>
       <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr"/>
@@ -3525,7 +3487,6 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr"/>
@@ -3545,7 +3506,6 @@
       <c r="O10" s="8" t="inlineStr"/>
       <c r="P10" s="8" t="inlineStr"/>
       <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr"/>
@@ -3565,7 +3525,6 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr"/>
@@ -3585,7 +3544,6 @@
       <c r="O12" s="8" t="inlineStr"/>
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr"/>
@@ -3605,7 +3563,6 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr"/>
@@ -3625,7 +3582,6 @@
       <c r="O14" s="8" t="inlineStr"/>
       <c r="P14" s="8" t="inlineStr"/>
       <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr"/>
@@ -3645,7 +3601,6 @@
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="8" t="inlineStr"/>
@@ -3665,23 +3620,19 @@
       <c r="O16" s="8" t="inlineStr"/>
       <c r="P16" s="8" t="inlineStr"/>
       <c r="Q16" s="8" t="inlineStr"/>
-      <c r="R16" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R204"/>
+  <autoFilter ref="A4:Q204"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Change type" error="Choose one of: Editorial, Wording, Mechanical, Rename, Add, Remove, Tier / DP, ID migration" promptTitle="Change type" prompt="Classify the change." type="list">
       <formula1>"Editorial,Wording,Mechanical,Rename,Add,Remove,Tier / DP,ID migration"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose one of: Proposed, Approved, Rejected, Deferred" promptTitle="Decision" prompt="Approval state for this change." type="list">
       <formula1>"Proposed,Approved,Rejected,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Playtest status" error="Choose one of: Not needed, Pending, Passed, Failed, N/A" promptTitle="Playtest status" prompt="Playtest evidence for mechanical changes." type="list">
-      <formula1>"Not needed,Pending,Passed,Failed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>

--- a/review/abilities/workbooks/28_Class_Unbalanced.xlsx
+++ b/review/abilities/workbooks/28_Class_Unbalanced.xlsx
@@ -731,21 +731,21 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>• Level 1: Drive through, charge, or rise fighting.</t>
+          <t>• Level 1: Charge, rage, or hurl.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>• Level 3: Break an obstruction, throw a creature, or shove back through pain.</t>
+          <t>• Level 3: Rampage, turn pain into Boons, or throw an ally over the line.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>• Level 7: Scatter enemies, wrench free and retaliate, or finish a push with a knockdown.</t>
+          <t>• Level 7: Break the ground, refuse to fall, or launch yourself as a missile.</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Force and control bruiser. Signatures push, throw, break objects and knock prone. The class has the highest HP contribution and the clearest 'meet the obstacle with everything' identity.</t>
+          <t>Force and displacement. Breakthrough, rage and throws; the class wins by changing the shape of the fight.</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Strong control and object interaction; Scatter the Line is a big AoE push; Fling the Captive is a great single-target throw. The class is straightforward to play.</t>
+          <t>Clear Ram, Rage and Hurler split. Strong movement, area control and risk/reward.</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Break Their Grip is a narrow anti-grapple Master pick; Crash Down is incremental; the class may lack a decisive single-target Master attack. Several signatures depend on Force or a push.</t>
+          <t>The Cannonball and Deathless Rage both invite self-destruction. Watch the self-damage and the one-turn window.</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Broaden Break Their Grip or give it a follow-up benefit. Consider a single-target Master strike that is not only a push. Keep the object-breaking niche; it is a real strength.</t>
+          <t>Playtest Earthbreaker's area and The Cannonball's recoil. Clarify whether Over the Top's thrown attack can trigger on the same turn.</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Shoulder Through; Wild Approach; Laugh at the Fall</t>
+          <t>Charge; Go Berserk; Grab and Hurl</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
@@ -862,7 +862,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Crush the Barrier; Fling the Captive; Raging Recoil</t>
+          <t>Rampage; Pain Feeds the Fire; Over the Top</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -882,7 +882,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Scatter the Line; Break Their Grip; Crash Down</t>
+          <t>Earthbreaker; Deathless Rage; The Cannonball</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
@@ -936,14 +936,10 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Several Master or Adept signature choices are simple riders or narrow utility: a 2-square push, a 2-square push plus move, an anti-grapple maneuver, a lockpicking card and a trail-concealment card.</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>For each, either add a second clause that broadens the moment (condition, ally benefit, alternate use) or accept it as a deliberate specialist pick and say so in the class guidance.</t>
-        </is>
-      </c>
+          <t>Redesign supersedes the earlier power-spike finding; re-check after playtest.</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
@@ -990,8 +986,8 @@
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="A20:D20"/>
@@ -1145,179 +1141,203 @@
     <row r="5" ht="66.5" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Laugh at the Fall</t>
+          <t>Charge</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>signature-unbalanced-laugh-at-the-fall</t>
+          <t>signature-unbalanced-shoulder-through</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Brawn</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Self, when you stand from Prone.</t>
+          <t>One creature at least 2 squares away and within your Speed, in a straight line.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Standing costs 1 square of movement instead of 2. After standing on your turn, gain 1 Boon to your next Force action or Main Action melee attack before that turn ends. This grants no ability to stand while movement is prohibited.</t>
+          <t>Move up to your Speed in a straight line toward the target. This movement provokes normally. If you end adjacent to it, make a Brawn roll against it. Weak: 2 physical damage, and push it 1 square. Standard: 3 physical damage, push it 2 squares, and it is Prone. Strong: 5 physical damage, push it 3 squares, and it is Prone. Resolve collisions normally. If you cannot move at least 2 squares, you cannot use this ability.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Standing costs 1 square of movement instead of 2. After standing on your turn, gain 1 Boon to your next Force action or Main Action melee attack before that turn ends. This grants no ability to stand while movement is prohibited.</t>
+          <t>Move up to your Speed in a straight line toward the target. This movement provokes normally. If you end adjacent to it, make a Brawn roll against it. Weak: 2 physical damage, and push it 1 square. Standard: 3 physical damage, push it 2 squares, and it is Prone. Strong: 5 physical damage, push it 3 squares, and it is Prone. Resolve collisions normally. If you cannot move at least 2 squares, you cannot use this ability.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Stand for 1 movement and gain a Boon to Force or a melee attack; good recovery and a fun image.</t>
+          <t>Ram: straight-line charge with damage, push and Prone.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the Boon applies if you stand via another effect and whether it stacks with other stand-cost reductions.</t>
+          <t>Approved: Main Action, Brawn. Charge 2+ squares; 2 + push 1 / 3 + push 2 + Prone / 5 + push 3 + Prone.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="66.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Shoulder Through</t>
+          <t>Go Berserk</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>signature-unbalanced-shoulder-through</t>
+          <t>signature-unbalanced-wild-approach</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>One creature pushed by your Force action.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Add 1 square to your Force push, on any result. You may then move 1 square directly toward the target without provoking if the square is free. This adds no grapple reduction or obstacle progress, and grants no attack.</t>
+          <t>Enter a rage until the end of the scene. While raging, you gain 1 Boon to attack rolls, have 1 Bane to defense rolls, and gain DR 1. You can end the rage at will. It also ends if you fall unconscious or enter Dying.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Add 1 square to your Force push, on any result. You may then move 1 square directly toward the target without provoking if the square is free. This adds no grapple reduction or obstacle progress, and grants no attack.</t>
+          <t>Enter a rage until the end of the scene. While raging, you gain 1 Boon to attack rolls, have 1 Bane to defense rolls, and gain DR 1. You can end the rage at will. It also ends if you fall unconscious or enter Dying.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Adds 1 square to a Force push and moves 1 toward the target; simple synergy.</t>
+          <t>Rage: 1 Boon to attacks, 1 Bane to defense, DR 1 for the scene.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Narrow if the character never uses Force. Consider allowing any push (for example Fling the Captive) or a 1-square move after any attack.</t>
+          <t>Approved: Maneuver. Rage: 1 Boon to attacks, 1 Bane to defense, DR 1 until the end of the scene.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Wild Approach</t>
+          <t>Grab and Hurl</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>signature-unbalanced-wild-approach</t>
+          <t>signature-unbalanced-laugh-at-the-fall</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Brawn</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Self; one visible enemy.</t>
+          <t>One adjacent creature your size or smaller.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Move up to 3 squares toward that enemy. This movement provokes normally. Gain 1 Boon to your next Main Action melee attack this turn. You must actually move at least 1 square to gain the Boon.</t>
+          <t>Make a Brawn roll against the target. Weak: it has Grappled 1. Standard: throw it up to 2 squares in a direction you choose; it lands Prone. Strong: throw it up to 3 squares in a direction you choose; it lands Prone and takes 2 physical damage. Resolve collisions normally. The throw ends any grapple from this ability.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Move up to 3 squares toward that enemy. This movement provokes normally. Gain 1 Boon to your next Main Action melee attack this turn. You must actually move at least 1 square to gain the Boon.</t>
+          <t>Make a Brawn roll against the target. Weak: it has Grappled 1. Standard: throw it up to 2 squares in a direction you choose; it lands Prone. Strong: throw it up to 3 squares in a direction you choose; it lands Prone and takes 2 physical damage. Resolve collisions normally. The throw ends any grapple from this ability.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Move 3 toward an enemy (provokes) and gain a Boon to your next melee attack; risky but strong.</t>
+          <t>Hurler: grapple or throw a creature, with Prone and collision damage.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the movement can pass through difficult terrain and whether the Boon applies to a signature attack (text says Main Action melee attack).</t>
+          <t>Approved: Main Action, Brawn. Grappled 1 / throw 2 + Prone / throw 3 + Prone + 2 damage.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M7"/>
@@ -1468,7 +1488,7 @@
     <row r="5" ht="129" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Crush the Barrier</t>
+          <t>Rampage</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -1488,167 +1508,183 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>One adjacent ordinary physical obstruction.</t>
+          <t>Self; a straight line up to your Speed.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Use Force to overcome the obstruction; the DA states its progress target and consequences before rolling.</t>
+          <t>This ability consumes your Main Action and your movement for the turn. Move up to your Speed in a straight line. Each enemy within 1 square of your path takes 2 physical damage and is pushed 1 square directly away from the path. Then make a Brawn roll against one enemy adjacent to you at the end of the movement. Weak: 3 physical damage. Standard: 4 physical damage, and it is Prone. Strong: 6 physical damage, and it is Prone. If you cannot move at least 2 squares in a straight line, you cannot use this ability. You cannot move again after the charge.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Use Force to overcome the obstruction; the DA states its progress target and consequences before rolling.
-• Weak: Add 2 progress.
-• Standard: Add 4 progress.
-• Strong: Add 6 progress.
-If this completes the target, you may move up to 2 squares through the opened route without provoking. This affects no creature or grapple and cannot force an impossible structure.</t>
+          <t>This ability consumes your Main Action and your movement for the turn. Move up to your Speed in a straight line. Each enemy within 1 square of your path takes 2 physical damage and is pushed 1 square directly away from the path. Then make a Brawn roll against one enemy adjacent to you at the end of the movement. Weak: 3 physical damage. Standard: 4 physical damage, and it is Prone. Strong: 6 physical damage, and it is Prone. If you cannot move at least 2 squares in a straight line, you cannot use this ability. You cannot move again after the charge.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Main Action Force vs an object with 2/4/6 progress and a 2-square move through the opening; strong utility.</t>
+          <t>Ram: full-turn straight-line charge that shoves a lane and ends in a slam.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the move is through the opened route only and whether it can target a creature's shield or armor (no, ordinary obstruction).</t>
+          <t>Approved: Main Action + movement. Charge a straight line; 2 + push 1 to enemies near the path, then 3 / 4 + Prone / 6 + Prone.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="141.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Fling the Captive</t>
+          <t>Pain Feeds the Fire</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>signature-unbalanced-fling-the-captive</t>
+          <t>signature-unbalanced-raging-recoil</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Main Action</t>
+          <t>Passive</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Brawn</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>One adjacent creature, whether or not you already grapple it.</t>
+          <t>Self, while raging.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Release any Grappled contribution you maintain on the target, then roll Brawn. You must have a Main Action before releasing; this card cannot be used while you are Grappled 3.</t>
+          <t>Each time you take damage while raging, gain 1 Boon to your next attack this round. Boons from this ability stack, up to the normal cap of 3.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Release any Grappled contribution you maintain on the target, then roll Brawn. You must have a Main Action before releasing; this card cannot be used while you are Grappled 3.
-• Weak: Deal 3 physical damage and push 1 square.
-• Standard: Deal 4 physical damage, push 2 squares and knock prone.
-• Strong: Deal 6 physical damage, push 3 squares and knock prone.
-No prior grappling card or existing hold is required. The DA judges whether your body can plausibly throw the target; use normal collision rules.</t>
+          <t>Each time you take damage while raging, gain 1 Boon to your next attack this round. Boons from this ability stack, up to the normal cap of 3.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Throw an adjacent creature for 3/4/6 damage, push and prone; strong control.</t>
+          <t>Rage: every hit taken adds 1 Boon to the next attack, up to the normal cap.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether 'whether or not you already grapple it' means you can throw an unwilling creature without a grapple check; the DA plausibility clause is broad.</t>
+          <t>Approved: Passive while raging. Each time you take damage, +1 Boon to your next attack this round, cap 3.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="66.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Raging Recoil</t>
+          <t>Over the Top</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>signature-unbalanced-raging-recoil</t>
+          <t>signature-unbalanced-fling-the-captive</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Reaction</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Brawn</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>One adjacent creature, after it damages you.</t>
+          <t>One willing ally your size or smaller within reach.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Push it up to 2 squares directly away, then you may move up to 2 squares toward it without provoking. Choose a legal route and free endpoint. The original damage remains; this adds no attack or direct damage beyond collisions.</t>
+          <t>Throw the ally up to 4 squares in a direction you choose, ignoring difficult terrain and passing over occupied squares. The ally must land standing in a free square. If it lands adjacent to an enemy, it may immediately make one Basic Melee attack against that enemy with 1 Boon. That attack is part of your action, not the ally's turn. The ally takes no damage from the throw.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Push it up to 2 squares directly away, then you may move up to 2 squares toward it without provoking. Choose a legal route and free endpoint. The original damage remains; this adds no attack or direct damage beyond collisions.</t>
+          <t>Throw the ally up to 4 squares in a direction you choose, ignoring difficult terrain and passing over occupied squares. The ally must land standing in a free square. If it lands adjacent to an enemy, it may immediately make one Basic Melee attack against that enemy with 1 Boon. That attack is part of your action, not the ally's turn. The ally takes no damage from the throw.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Reaction push 2 and move 2 toward the attacker; strong positioning.</t>
+          <t>Hurler: throw a willing ally 4 squares; it can make a Boon Basic Melee on landing.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the movement can be used if the attacker is out of reach and whether it provokes (no).</t>
+          <t>Approved: Maneuver, Brawn. Throw an ally up to 4 squares; if it lands adjacent to an enemy, it makes one Basic Melee with 1 Boon.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M7"/>
@@ -1799,71 +1835,79 @@
     <row r="5" ht="66.5" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Break Their Grip</t>
+          <t>Earthbreaker</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>signature-unbalanced-break-their-grip</t>
+          <t>signature-unbalanced-scatter-the-line</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Brawn</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Self while Grappled 1 or 2, and one adjacent creature contributing to that grapple.</t>
+          <t>Self; each enemy within 2 squares.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Reduce your Grappled rating by up to 2, removing actual contributions you choose and the matching burden on those grapplers. Then push one contributing adjacent grappler up to 2 squares directly away and move 1 square without provoking if now able.</t>
+          <t>Make a Brawn roll and apply it to every enemy in range. Weak: 2 physical damage, and push 1 square directly away from you. Standard: 4 physical damage, push 2 squares, and it is Prone. Strong: 6 physical damage, push 3 squares, and it is Prone and Dazed 1. Structures and unattended objects in the area take double damage. Resolve collisions normally. This does not move you.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Reduce your Grappled rating by up to 2, removing actual contributions you choose and the matching burden on those grapplers. Then push one contributing adjacent grappler up to 2 squares directly away and move 1 square without provoking if now able. You must have retained a Maneuver; at Grappled 3 you cannot use this card.</t>
+          <t>Make a Brawn roll and apply it to every enemy in range. Weak: 2 physical damage, and push 1 square directly away from you. Standard: 4 physical damage, push 2 squares, and it is Prone. Strong: 6 physical damage, push 3 squares, and it is Prone and Dazed 1. Structures and unattended objects in the area take double damage. Resolve collisions normally. This does not move you.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Maneuver reduce Grappled by 2, push a grappler 2 and move 1; narrow anti-grapple Master.</t>
+          <t>Ram: ground-slam shockwave; area damage, push, Prone, double damage to structures.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Broaden to also reduce Restrained or Prone, or grant a Boon against the grappler; otherwise it competes poorly with Scatter the Line and Crash Down.</t>
+          <t>Approved: Main Action, Brawn. Each enemy within 2: 2 + push 1 / 4 + push 2 + Prone / 6 + push 3 + Prone + Dazed 1.</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Narrow Master</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="79" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Crash Down</t>
+          <t>Deathless Rage</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>signature-unbalanced-crash-down</t>
+          <t>signature-unbalanced-break-their-grip</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -1873,56 +1917,64 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>One creature pushed by your Main Action attack or Force action.</t>
+          <t>Self, while raging.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>After that push resolves, you may knock the target prone even if it did not strike an obstruction. Then you may move 1 square toward it without provoking if a legal free square is available. This adds no collision damage and cannot create numbered Prone.</t>
+          <t>Once per scene, when you would be reduced to 0 HP while raging, you remain at 1 HP instead. You keep fighting until the end of your next turn. If you are not healed above 0 HP by then, you fall to 0 HP and begin Dying. This does not prevent the wound or the death marks.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>After that push resolves, you may knock the target prone even if it did not strike an obstruction. Then you may move 1 square toward it without provoking if a legal free square is available. This adds no collision damage and cannot create numbered Prone.</t>
+          <t>Once per scene, when you would be reduced to 0 HP while raging, you remain at 1 HP instead. You keep fighting until the end of your next turn. If you are not healed above 0 HP by then, you fall to 0 HP and begin Dying. This does not prevent the wound or the death marks.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Passive knock prone after any push; strong combo with Force and Shoulder Through.</t>
+          <t>Rage: once per scene, stay at 1 HP for one turn instead of falling; heal or fall.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether it applies to pushes from any source (text says Main Action attack or Force) and whether it can knock a flying creature prone.</t>
+          <t>Approved: Passive while raging. Once per scene, at 0 HP remain at 1 HP until the end of your next turn; if not healed, fall.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="116.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Scatter the Line</t>
+          <t>The Cannonball</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>signature-unbalanced-scatter-the-line</t>
+          <t>signature-unbalanced-crash-down</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1937,45 +1989,49 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Every enemy adjacent when you begin.</t>
+          <t>One creature within 4 squares.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Roll Brawn once using the least favorable net Boons/Banes among the targets.</t>
+          <t>Move up to 4 squares in a straight line toward the target, ignoring difficult terrain. If you end adjacent to it, make a Brawn roll. Weak: 4 physical damage to the target. You take 3 physical damage and are Prone. Standard: 8 physical damage, and the target is Prone. You take 2 physical damage. Strong: 12 physical damage, and the target is Prone and Dazed 1. You take 1 physical damage and are Dazed 1. If you cannot move at least 2 squares, you cannot use this ability. Resolve collisions normally.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Roll Brawn once using the least favorable net Boons/Banes among the targets.
-• Weak: Push each 2 squares directly away from you.
-• Standard: Push each 3 squares.
-• Strong: Push each 4 squares and knock each prone.
-Resolve the targets in an order you choose. No direct damage; normal collisions apply.</t>
+          <t>Move up to 4 squares in a straight line toward the target, ignoring difficult terrain. If you end adjacent to it, make a Brawn roll. Weak: 4 physical damage to the target. You take 3 physical damage and are Prone. Standard: 8 physical damage, and the target is Prone. You take 2 physical damage. Strong: 12 physical damage, and the target is Prone and Dazed 1. You take 1 physical damage and are Dazed 1. If you cannot move at least 2 squares, you cannot use this ability. Resolve collisions normally.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Master AoE push 2/3/4 and prone on Strong; strong control and a clear capstone.</t>
+          <t>Hurler: launch yourself for 4/8/12 damage; always take recoil damage and risk Prone or Dazed.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether 'every enemy adjacent when you begin' includes allies (no) and whether pushes resolve simultaneously or in an order you choose.</t>
+          <t>Approved: Main Action, Brawn. Launch 4 squares: 4 / 8 + Prone / 12 + Prone + Dazed 1; you take 3+Prone / 2 / 1+Dazed 1.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M7"/>
@@ -2124,535 +2180,589 @@
       </c>
     </row>
     <row r="5" ht="66.5" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A5" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Laugh at the Fall</t>
+          <t>Charge</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
+          <t>signature-unbalanced-shoulder-through</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Brawn</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>One creature at least 2 squares away and within your Speed, in a straight line.</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Move up to your Speed in a straight line toward the target. This movement provokes normally. If you end adjacent to it, make a Brawn roll against it. Weak: 2 physical damage, and push it 1 square. Standard: 3 physical damage, push it 2 squares, and it is Prone. Strong: 5 physical damage, push it 3 squares, and it is Prone. Resolve collisions normally. If you cannot move at least 2 squares, you cannot use this ability.</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Ram: straight-line charge with damage, push and Prone.</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Approved: Main Action, Brawn. Charge 2+ squares; 2 + push 1 / 3 + push 2 + Prone / 5 + push 3 + Prone.</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66.5" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Go Berserk</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-wild-approach</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>None (no roll)</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Self.</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Enter a rage until the end of the scene. While raging, you gain 1 Boon to attack rolls, have 1 Bane to defense rolls, and gain DR 1. You can end the rage at will. It also ends if you fall unconscious or enter Dying.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Rage: 1 Boon to attacks, 1 Bane to defense, DR 1 for the scene.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Approved: Maneuver. Rage: 1 Boon to attacks, 1 Bane to defense, DR 1 until the end of the scene.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Grab and Hurl</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
           <t>signature-unbalanced-laugh-at-the-fall</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Brawn</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>One adjacent creature your size or smaller.</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Make a Brawn roll against the target. Weak: it has Grappled 1. Standard: throw it up to 2 squares in a direction you choose; it lands Prone. Strong: throw it up to 3 squares in a direction you choose; it lands Prone and takes 2 physical damage. Resolve collisions normally. The throw ends any grapple from this ability.</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Hurler: grapple or throw a creature, with Prone and collision damage.</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Approved: Main Action, Brawn. Grappled 1 / throw 2 + Prone / throw 3 + Prone + 2 damage.</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="41.5" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Rampage</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crush-the-barrier</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Brawn</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Self; a straight line up to your Speed.</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>This ability consumes your Main Action and your movement for the turn. Move up to your Speed in a straight line. Each enemy within 1 square of your path takes 2 physical damage and is pushed 1 square directly away from the path. Then make a Brawn roll against one enemy adjacent to you at the end of the movement. Weak: 3 physical damage. Standard: 4 physical damage, and it is Prone. Strong: 6 physical damage, and it is Prone. If you cannot move at least 2 squares in a straight line, you cannot use this ability. You cannot move again after the charge.</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Ram: full-turn straight-line charge that shoves a lane and ends in a slam.</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Approved: Main Action + movement. Charge a straight line; 2 + push 1 to enemies near the path, then 3 / 4 + Prone / 6 + Prone.</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Pain Feeds the Fire</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-raging-recoil</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Self, when you stand from Prone.</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Standing costs 1 square of movement instead of 2. After standing on your turn, gain 1 Boon to your next Force action or Main Action melee attack before that turn ends. This grants no ability to stand while movement is prohibited.</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Stand for 1 movement and gain a Boon to Force or a melee attack; good recovery and a fun image.</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Clarify whether the Boon applies if you stand via another effect and whether it stacks with other stand-cost reductions.</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6" ht="66.5" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Shoulder Through</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>signature-unbalanced-shoulder-through</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>None (no roll)</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Self, while raging.</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Each time you take damage while raging, gain 1 Boon to your next attack this round. Boons from this ability stack, up to the normal cap of 3.</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Rage: every hit taken adds 1 Boon to the next attack, up to the normal cap.</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Approved: Passive while raging. Each time you take damage, +1 Boon to your next attack this round, cap 3.</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66.5" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Over the Top</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-fling-the-captive</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Brawn</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>One willing ally your size or smaller within reach.</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Throw the ally up to 4 squares in a direction you choose, ignoring difficult terrain and passing over occupied squares. The ally must land standing in a free square. If it lands adjacent to an enemy, it may immediately make one Basic Melee attack against that enemy with 1 Boon. That attack is part of your action, not the ally's turn. The ally takes no damage from the throw.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Hurler: throw a willing ally 4 squares; it can make a Boon Basic Melee on landing.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Approved: Maneuver, Brawn. Throw an ally up to 4 squares; if it lands adjacent to an enemy, it makes one Basic Melee with 1 Boon.</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66.5" customHeight="1">
+      <c r="A11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Earthbreaker</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-scatter-the-line</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Brawn</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Self; each enemy within 2 squares.</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Make a Brawn roll and apply it to every enemy in range. Weak: 2 physical damage, and push 1 square directly away from you. Standard: 4 physical damage, push 2 squares, and it is Prone. Strong: 6 physical damage, push 3 squares, and it is Prone and Dazed 1. Structures and unattended objects in the area take double damage. Resolve collisions normally. This does not move you.</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Ram: ground-slam shockwave; area damage, push, Prone, double damage to structures.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Approved: Main Action, Brawn. Each enemy within 2: 2 + push 1 / 4 + push 2 + Prone / 6 + push 3 + Prone + Dazed 1.</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="79" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Deathless Rage</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-break-their-grip</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>One creature pushed by your Force action.</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Add 1 square to your Force push, on any result. You may then move 1 square directly toward the target without provoking if the square is free. This adds no grapple reduction or obstacle progress, and grants no attack.</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>Adds 1 square to a Force push and moves 1 toward the target; simple synergy.</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>Narrow if the character never uses Force. Consider allowing any push (for example Fling the Captive) or a 1-square move after any attack.</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Wild Approach</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>signature-unbalanced-wild-approach</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Maneuver</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Self; one visible enemy.</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Move up to 3 squares toward that enemy. This movement provokes normally. Gain 1 Boon to your next Main Action melee attack this turn. You must actually move at least 1 square to gain the Boon.</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Move 3 toward an enemy (provokes) and gain a Boon to your next melee attack; risky but strong.</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Clarify whether the movement can pass through difficult terrain and whether the Boon applies to a signature attack (text says Main Action melee attack).</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8" ht="41.5" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Crush the Barrier</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>signature-unbalanced-crush-the-barrier</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>None (no roll)</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Self, while raging.</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Once per scene, when you would be reduced to 0 HP while raging, you remain at 1 HP instead. You keep fighting until the end of your next turn. If you are not healed above 0 HP by then, you fall to 0 HP and begin Dying. This does not prevent the wound or the death marks.</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Rage: once per scene, stay at 1 HP for one turn instead of falling; heal or fall.</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Approved: Passive while raging. Once per scene, at 0 HP remain at 1 HP until the end of your next turn; if not healed, fall.</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="41.5" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>The Cannonball</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crash-down</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>Main Action</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Brawn</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>One adjacent ordinary physical obstruction.</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>Use Force to overcome the obstruction; the DA states its progress target and consequences before rolling.</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>Main Action Force vs an object with 2/4/6 progress and a 2-square move through the opening; strong utility.</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>Clarify whether the move is through the opened route only and whether it can target a creature's shield or armor (no, ordinary obstruction).</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr"/>
-      <c r="M8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Fling the Captive</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>signature-unbalanced-fling-the-captive</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Main Action</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Brawn</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>One adjacent creature, whether or not you already grapple it.</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Release any Grappled contribution you maintain on the target, then roll Brawn. You must have a Main Action before releasing; this card cannot be used while you are Grappled 3.</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Throw an adjacent creature for 3/4/6 damage, push and prone; strong control.</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Clarify whether 'whether or not you already grapple it' means you can throw an unwilling creature without a grapple check; the DA plausibility clause is broad.</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="66.5" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Raging Recoil</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>signature-unbalanced-raging-recoil</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Reaction</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>One adjacent creature, after it damages you.</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Push it up to 2 squares directly away, then you may move up to 2 squares toward it without provoking. Choose a legal route and free endpoint. The original damage remains; this adds no attack or direct damage beyond collisions.</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>Reaction push 2 and move 2 toward the attacker; strong positioning.</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>Clarify whether the movement can be used if the attacker is out of reach and whether it provokes (no).</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr"/>
-      <c r="M10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11" ht="66.5" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Break Their Grip</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>signature-unbalanced-break-their-grip</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Maneuver</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Self while Grappled 1 or 2, and one adjacent creature contributing to that grapple.</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Reduce your Grappled rating by up to 2, removing actual contributions you choose and the matching burden on those grapplers. Then push one contributing adjacent grappler up to 2 squares directly away and move 1 square without provoking if now able.</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Maneuver reduce Grappled by 2, push a grappler 2 and move 1; narrow anti-grapple Master.</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Broaden to also reduce Restrained or Prone, or grant a Boon against the grappler; otherwise it competes poorly with Scatter the Line and Crash Down.</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>Narrow Master</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr"/>
-      <c r="M11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12" ht="79" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Crash Down</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>signature-unbalanced-crash-down</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>One creature pushed by your Main Action attack or Force action.</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>After that push resolves, you may knock the target prone even if it did not strike an obstruction. Then you may move 1 square toward it without provoking if a legal free square is available. This adds no collision damage and cannot create numbered Prone.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>Passive knock prone after any push; strong combo with Force and Shoulder Through.</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>Clarify whether it applies to pushes from any source (text says Main Action attack or Force) and whether it can knock a flying creature prone.</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr"/>
-      <c r="M12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13" ht="41.5" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Scatter the Line</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>signature-unbalanced-scatter-the-line</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Main Action</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Brawn</t>
-        </is>
-      </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Every enemy adjacent when you begin.</t>
+          <t>One creature within 4 squares.</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Roll Brawn once using the least favorable net Boons/Banes among the targets.</t>
+          <t>Move up to 4 squares in a straight line toward the target, ignoring difficult terrain. If you end adjacent to it, make a Brawn roll. Weak: 4 physical damage to the target. You take 3 physical damage and are Prone. Standard: 8 physical damage, and the target is Prone. You take 2 physical damage. Strong: 12 physical damage, and the target is Prone and Dazed 1. You take 1 physical damage and are Dazed 1. If you cannot move at least 2 squares, you cannot use this ability. Resolve collisions normally.</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Master AoE push 2/3/4 and prone on Strong; strong control and a clear capstone.</t>
+          <t>Hurler: launch yourself for 4/8/12 damage; always take recoil damage and risk Prone or Dazed.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether 'every enemy adjacent when you begin' includes allies (no) and whether pushes resolve simultaneously or in an order you choose.</t>
+          <t>Approved: Main Action, Brawn. Launch 4 squares: 4 / 8 + Prone / 12 + Prone + Dazed 1; you take 3+Prone / 2 / 1+Dazed 1.</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M13"/>
@@ -2790,7 +2900,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1</v>
@@ -2799,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>0</v>
@@ -2823,16 +2933,16 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8" t="n">
+      <c r="E7" s="8" t="n">
         <v>1</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>2</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>0</v>
@@ -2859,13 +2969,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>0</v>
@@ -2943,16 +3053,16 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
@@ -2964,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
@@ -2974,13 +3084,13 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>2</v>
@@ -2989,13 +3099,13 @@
         <v>0</v>
       </c>
       <c r="G13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="I13" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1">
@@ -3005,19 +3115,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="F14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>0</v>
@@ -3026,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -3039,14 +3149,14 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>• Break Their Grip is a narrow anti-grapple Master pick; Crash Down is incremental; the class may lack a decisive single-target Master attack. Several signatures depend on Force or a push.</t>
+          <t>The Ram and Hurler both want the Main Action; the Rage is the passive layer. Watch for a one-note turn rotation.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>• Broaden Break Their Grip or give it a follow-up benefit. Consider a single-target Master strike that is not only a push. Keep the object-breaking niche; it is a real strength.</t>
+          <t>The Cannonball's recoil is the balance valve. Check that the self-damage and Dazed are actually landing in play.</t>
         </is>
       </c>
     </row>
@@ -3186,41 +3296,17 @@
     <row r="5" ht="29" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Break Their Grip</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>signature-unbalanced-break-their-grip</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Narrow Master</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Anti-grapple only; competes with broad Master control options.</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Broaden to reduce another condition or grant a follow-up benefit.</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
+          <t>No row-level flags for this class. Use the design questions below.</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
       <c r="J5" s="7" t="inlineStr"/>
     </row>
   </sheetData>
@@ -3269,7 +3355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3394,232 +3480,5495 @@
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr"/>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr"/>
-      <c r="K5" s="7" t="inlineStr"/>
-      <c r="L5" s="7" t="inlineStr"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>CHG-UNB-001</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-shoulder-through</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-shoulder-through.md</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Shoulder Through</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>New title names the Ram effect.</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M5" s="7" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O5" s="7" t="inlineStr"/>
-      <c r="P5" s="7" t="inlineStr"/>
-      <c r="Q5" s="7" t="inlineStr"/>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="8" t="inlineStr"/>
-      <c r="B6" s="8" t="inlineStr"/>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr"/>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>CHG-UNB-002</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-shoulder-through</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-shoulder-through.md</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>You drive your shoulder into the resistance and keep pushing after the first step gives way.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>You lower your shoulder and let the distance do the work.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="7" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr"/>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>CHG-UNB-003</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-shoulder-through</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-shoulder-through.md</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O7" s="7" t="inlineStr"/>
-      <c r="P7" s="7" t="inlineStr"/>
-      <c r="Q7" s="7" t="inlineStr"/>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="8" t="inlineStr"/>
-      <c r="B8" s="8" t="inlineStr"/>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr"/>
-      <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr"/>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>CHG-UNB-004</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-shoulder-through</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-shoulder-through.md</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Brawn</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M8" s="8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O8" s="8" t="inlineStr"/>
-      <c r="P8" s="8" t="inlineStr"/>
-      <c r="Q8" s="8" t="inlineStr"/>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="7" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>CHG-UNB-005</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-shoulder-through</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-shoulder-through.md</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>One creature pushed by your Force action.</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>One creature at least 2 squares away and within your Speed, in a straight line.</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O9" s="7" t="inlineStr"/>
-      <c r="P9" s="7" t="inlineStr"/>
-      <c r="Q9" s="7" t="inlineStr"/>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="8" t="inlineStr"/>
-      <c r="B10" s="8" t="inlineStr"/>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="inlineStr"/>
-      <c r="J10" s="8" t="inlineStr"/>
-      <c r="K10" s="8" t="inlineStr"/>
-      <c r="L10" s="8" t="inlineStr"/>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>CHG-UNB-006</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-shoulder-through</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-shoulder-through.md</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Add 1 square to your Force push, on any result. You may then move 1 square directly toward the target without provoking if the square is free. This adds no grapple reduction or obstacle progress, and grants no attack.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Move up to your Speed in a straight line toward the target. This movement provokes normally. If you end adjacent to it, make a Brawn roll against it. Weak: 2 physical damage, and push it 1 square. Standard: 3 physical damage, push it 2 squares, and it is Prone. Strong: 5 physical damage, push it 3 squares, and it is Prone. Resolve collisions normally. If you cannot move at least 2 squares, you cannot use this ability.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Ram design.</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M10" s="8" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O10" s="8" t="inlineStr"/>
-      <c r="P10" s="8" t="inlineStr"/>
-      <c r="Q10" s="8" t="inlineStr"/>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="7" t="inlineStr"/>
-      <c r="B11" s="7" t="inlineStr"/>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr"/>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>CHG-UNB-007</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-shoulder-through</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-shoulder-through.md</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Immediate additional push and following step.</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Immediate.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M11" s="7" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O11" s="7" t="inlineStr"/>
-      <c r="P11" s="7" t="inlineStr"/>
-      <c r="Q11" s="7" t="inlineStr"/>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="8" t="inlineStr"/>
-      <c r="B12" s="8" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
-      <c r="L12" s="8" t="inlineStr"/>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>CHG-UNB-008</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-shoulder-through</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-shoulder-through.md</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Skill / Control / Movement</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Movement / Control</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M12" s="8" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O12" s="8" t="inlineStr"/>
-      <c r="P12" s="8" t="inlineStr"/>
-      <c r="Q12" s="8" t="inlineStr"/>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="7" t="inlineStr"/>
-      <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr"/>
-      <c r="J13" s="7" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>CHG-UNB-009</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-shoulder-through</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-shoulder-through.md</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Once on your turn.</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O13" s="7" t="inlineStr"/>
-      <c r="P13" s="7" t="inlineStr"/>
-      <c r="Q13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="8" t="inlineStr"/>
-      <c r="B14" s="8" t="inlineStr"/>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="8" t="inlineStr"/>
-      <c r="J14" s="8" t="inlineStr"/>
-      <c r="K14" s="8" t="inlineStr"/>
-      <c r="L14" s="8" t="inlineStr"/>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>CHG-UNB-010</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-laugh-at-the-fall</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Grab and Hurl</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-laugh-at-the-fall.md</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Laugh at the Fall</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Grab and Hurl</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>New title names the Hurler effect.</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M14" s="8" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O14" s="8" t="inlineStr"/>
-      <c r="P14" s="8" t="inlineStr"/>
-      <c r="Q14" s="8" t="inlineStr"/>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="7" t="inlineStr"/>
-      <c r="B15" s="7" t="inlineStr"/>
-      <c r="C15" s="7" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr"/>
-      <c r="J15" s="7" t="inlineStr"/>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>CHG-UNB-011</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-laugh-at-the-fall</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Grab and Hurl</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-laugh-at-the-fall.md</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>You spit out the dust, bark a laugh and surge to your feet before the enemy has finished enjoying the sight.</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>You get a hand on them, and the room becomes a weapon.</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O15" s="7" t="inlineStr"/>
-      <c r="P15" s="7" t="inlineStr"/>
-      <c r="Q15" s="7" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="8" t="inlineStr"/>
-      <c r="B16" s="8" t="inlineStr"/>
-      <c r="C16" s="8" t="inlineStr"/>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="8" t="inlineStr"/>
-      <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="8" t="inlineStr"/>
-      <c r="J16" s="8" t="inlineStr"/>
-      <c r="K16" s="8" t="inlineStr"/>
-      <c r="L16" s="8" t="inlineStr"/>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>CHG-UNB-012</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-laugh-at-the-fall</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Grab and Hurl</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-laugh-at-the-fall.md</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M16" s="8" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O16" s="8" t="inlineStr"/>
-      <c r="P16" s="8" t="inlineStr"/>
-      <c r="Q16" s="8" t="inlineStr"/>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CHG-UNB-013</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-laugh-at-the-fall</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Grab and Hurl</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-laugh-at-the-fall.md</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Brawn</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CHG-UNB-014</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-laugh-at-the-fall</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Grab and Hurl</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-laugh-at-the-fall.md</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Self, when you stand from Prone.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>One adjacent creature your size or smaller.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CHG-UNB-015</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-laugh-at-the-fall</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Grab and Hurl</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-laugh-at-the-fall.md</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Standing costs 1 square of movement instead of 2. After standing on your turn, gain 1 Boon to your next Force action or Main Action melee attack before that turn ends. This grants no ability to stand while movement is prohibited.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Make a Brawn roll against the target. Weak: it has Grappled 1. Standard: throw it up to 2 squares in a direction you choose; it lands Prone. Strong: throw it up to 3 squares in a direction you choose; it lands Prone and takes 2 physical damage. Resolve collisions normally. The throw ends any grapple from this ability.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Hurler design.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CHG-UNB-016</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-laugh-at-the-fall</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Grab and Hurl</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-laugh-at-the-fall.md</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Standing cost is always changed; the Boon expires when used or this turn ends.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Immediate; Grappled and Prone use their normal rules.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CHG-UNB-017</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-laugh-at-the-fall</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Grab and Hurl</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-laugh-at-the-fall.md</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Control / Movement</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHG-UNB-018</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-laugh-at-the-fall</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Grab and Hurl</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-laugh-at-the-fall.md</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>The Boon can be gained once on your turn; repeated standing does not stack it.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CHG-UNB-019</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-wild-approach</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Go Berserk</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-wild-approach.md</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Wild Approach</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Go Berserk</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>New title names the Rage effect.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CHG-UNB-020</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-wild-approach</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Go Berserk</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-wild-approach.md</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>You roar and charge into the opening, arriving with your whole weight behind the next blow.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>You stop listening to the part of you that wants to stay alive.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CHG-UNB-021</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-wild-approach</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Go Berserk</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-wild-approach.md</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Self; one visible enemy.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Self.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CHG-UNB-022</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-wild-approach</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Go Berserk</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-wild-approach.md</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Move up to 3 squares toward that enemy. This movement provokes normally. Gain 1 Boon to your next Main Action melee attack this turn. You must actually move at least 1 square to gain the Boon.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Enter a rage until the end of the scene. While raging, you gain 1 Boon to attack rolls, have 1 Bane to defense rolls, and gain DR 1. You can end the rage at will. It also ends if you fall unconscious or enter Dying.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Rage design.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CHG-UNB-023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-wild-approach</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Go Berserk</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-wild-approach.md</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Movement is immediate; Boon expires when used or this turn ends.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Until the end of the scene, or until you end it.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CHG-UNB-024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-wild-approach</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Go Berserk</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-wild-approach.md</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Defense</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CHG-UNB-025</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-wild-approach</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Go Berserk</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-wild-approach.md</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Once per scene.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CHG-UNB-026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crush-the-barrier</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rampage</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crush-the-barrier.md</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Crush the Barrier</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Rampage</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>New title names the Ram effect.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CHG-UNB-027</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crush-the-barrier</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rampage</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crush-the-barrier.md</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>You hear the first crack, plant your feet and drive through the weak point with another heave.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>You do not stop at the first body.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CHG-UNB-028</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crush-the-barrier</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Rampage</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crush-the-barrier.md</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>One adjacent ordinary physical obstruction.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Self; a straight line up to your Speed.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CHG-UNB-029</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crush-the-barrier</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Rampage</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crush-the-barrier.md</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Use Force to overcome the obstruction; the DA states its progress target and consequences before rolling. - **Weak:** Add 2 progress. - **Standard:** Add 4 progress. - **Strong:** Add 6 progress. If this completes the target, you may move up to 2 squares through the opened route without provoking. This affects no creature or grapple and cannot force an impossible structure.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>This ability consumes your Main Action and your movement for the turn. Move up to your Speed in a straight line. Each enemy within 1 square of your path takes 2 physical damage and is pushed 1 square directly away from the path. Then make a Brawn roll against one enemy adjacent to you at the end of the movement. Weak: 3 physical damage. Standard: 4 physical damage, and it is Prone. Strong: 6 physical damage, and it is Prone. If you cannot move at least 2 squares in a straight line, you cannot use this ability. You cannot move again after the charge.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Ram design.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CHG-UNB-030</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crush-the-barrier</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Rampage</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crush-the-barrier.md</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Progress and any completed opening persist; movement is immediate.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Immediate.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CHG-UNB-031</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crush-the-barrier</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Rampage</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crush-the-barrier.md</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Skill / Utility / Movement</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Movement / Control</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CHG-UNB-032</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crush-the-barrier</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Rampage</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crush-the-barrier.md</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Once per scene.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CHG-UNB-033</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-raging-recoil</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pain Feeds the Fire</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-raging-recoil.md</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Raging Recoil</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Pain Feeds the Fire</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>New title names the Rage effect.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CHG-UNB-034</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-raging-recoil</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pain Feeds the Fire</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-raging-recoil.md</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>You snarl at the pain and shove back into the attacker, following the stumble with another aggressive step.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>The hit lands, and you smile.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CHG-UNB-035</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-raging-recoil</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pain Feeds the Fire</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-raging-recoil.md</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Reaction</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CHG-UNB-036</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-raging-recoil</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pain Feeds the Fire</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-raging-recoil.md</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>One adjacent creature, after it damages you.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Self, while raging.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CHG-UNB-037</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-raging-recoil</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pain Feeds the Fire</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-raging-recoil.md</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Push it up to 2 squares directly away, then you may move up to 2 squares toward it without provoking. Choose a legal route and free endpoint. The original damage remains; this adds no attack or direct damage beyond collisions.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Each time you take damage while raging, gain 1 Boon to your next attack this round. Boons from this ability stack, up to the normal cap of 3.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Rage design.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CHG-UNB-038</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-raging-recoil</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pain Feeds the Fire</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-raging-recoil.md</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Immediate push and movement.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>While raging.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CHG-UNB-039</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-raging-recoil</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pain Feeds the Fire</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-raging-recoil.md</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Skill / Control / Movement</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Skill / Attack</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CHG-UNB-040</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-raging-recoil</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pain Feeds the Fire</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-raging-recoil.md</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>While raging; normal Boon cap applies.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CHG-UNB-041</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-fling-the-captive</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Over the Top</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-fling-the-captive.md</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Fling the Captive</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Over the Top</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>New title names the Hurler effect.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CHG-UNB-042</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-fling-the-captive</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Over the Top</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-fling-the-captive.md</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>You catch the struggling body, turn hard at the hips and release the whole tangle in a violent throw.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>You take your companion by the belt and the collar and send them over the line.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHG-UNB-043</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-fling-the-captive</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Over the Top</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-fling-the-captive.md</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CHG-UNB-044</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-fling-the-captive</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Over the Top</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-fling-the-captive.md</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>One adjacent creature, whether or not you already grapple it.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>One willing ally your size or smaller within reach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CHG-UNB-045</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-fling-the-captive</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Over the Top</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-fling-the-captive.md</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Release any Grappled contribution you maintain on the target, then roll Brawn. You must have a Main Action before releasing; this card cannot be used while you are Grappled 3. - **Weak:** Deal 3 physical damage and push 1 square. - **Standard:** Deal 4 physical damage, push 2 squares and knock prone. - **Strong:** Deal 6 physical damage, push 3 squares and knock prone. No prior grappling card or existing hold is required. The DA judges whether your body can plausibly throw the target; use normal collision rules.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Throw the ally up to 4 squares in a direction you choose, ignoring difficult terrain and passing over occupied squares. The ally must land standing in a free square. If it lands adjacent to an enemy, it may immediately make one Basic Melee attack against that enemy with 1 Boon. That attack is part of your action, not the ally's turn. The ally takes no damage from the throw.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Hurler design.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CHG-UNB-046</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-fling-the-captive</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Over the Top</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-fling-the-captive.md</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Immediate damage, push and Prone.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Immediate.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CHG-UNB-047</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-fling-the-captive</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Over the Top</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-fling-the-captive.md</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Control</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Skill / Movement / Support</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CHG-UNB-048</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-break-their-grip</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Deathless Rage</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-break-their-grip.md</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Break Their Grip</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Deathless Rage</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>New title names the Rage effect.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CHG-UNB-049</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-break-their-grip</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Deathless Rage</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-break-their-grip.md</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>You wrench your shoulders free and crash back against the hands that tried to hold you.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>You should be down. You have not noticed.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CHG-UNB-050</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-break-their-grip</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Deathless Rage</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-break-their-grip.md</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CHG-UNB-051</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-break-their-grip</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Deathless Rage</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-break-their-grip.md</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Self while Grappled 1 or 2, and one adjacent creature contributing to that grapple.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Self, while raging.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CHG-UNB-052</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-break-their-grip</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Deathless Rage</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-break-their-grip.md</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Reduce your Grappled rating by up to 2, removing actual contributions you choose and the matching burden on those grapplers. Then push one contributing adjacent grappler up to 2 squares directly away and move 1 square without provoking if now able. You must have retained a Maneuver; at Grappled 3 you cannot use this card.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Once per scene, when you would be reduced to 0 HP while raging, you remain at 1 HP instead. You keep fighting until the end of your next turn. If you are not healed above 0 HP by then, you fall to 0 HP and begin Dying. This does not prevent the wound or the death marks.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Rage design.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CHG-UNB-053</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-break-their-grip</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Deathless Rage</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-break-their-grip.md</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Immediate release, push and possible step.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Until the end of your next turn.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CHG-UNB-054</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-break-their-grip</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Deathless Rage</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-break-their-grip.md</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Skill / Control / Movement</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Skill / Recovery / Defense</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CHG-UNB-055</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-break-their-grip</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Deathless Rage</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-break-their-grip.md</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Once per scene.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CHG-UNB-056</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-scatter-the-line</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Earthbreaker</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-scatter-the-line.md</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Scatter the Line</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Earthbreaker</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>New title names the Ram effect.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CHG-UNB-057</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-scatter-the-line</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Earthbreaker</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-scatter-the-line.md</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>You throw your arms wide and drive into the bodies around you, sending the whole front rank stumbling away.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>You stop charging, plant both hands in the ground, and let the earth answer.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CHG-UNB-058</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-scatter-the-line</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Earthbreaker</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-scatter-the-line.md</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Every enemy adjacent when you begin.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Self; each enemy within 2 squares.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CHG-UNB-059</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-scatter-the-line</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Earthbreaker</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-scatter-the-line.md</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Roll Brawn once using the least favorable net Boons/Banes among the targets. - **Weak:** Push each 2 squares directly away from you. - **Standard:** Push each 3 squares. - **Strong:** Push each 4 squares and knock each prone. Resolve the targets in an order you choose. No direct damage; normal collisions apply.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Make a Brawn roll and apply it to every enemy in range. Weak: 2 physical damage, and push 1 square directly away from you. Standard: 4 physical damage, push 2 squares, and it is Prone. Strong: 6 physical damage, push 3 squares, and it is Prone and Dazed 1. Structures and unattended objects in the area take double damage. Resolve collisions normally. This does not move you.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Ram design.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CHG-UNB-060</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-scatter-the-line</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Earthbreaker</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-scatter-the-line.md</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Immediate displacement and Prone.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Immediate.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CHG-UNB-061</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-scatter-the-line</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Earthbreaker</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-scatter-the-line.md</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Skill / Control</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Control</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CHG-UNB-062</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-scatter-the-line</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Earthbreaker</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-scatter-the-line.md</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Once per scene.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CHG-UNB-063</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crash-down</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>The Cannonball</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crash-down.md</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Crash Down</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>The Cannonball</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>New title names the Hurler effect.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CHG-UNB-064</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crash-down</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>The Cannonball</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crash-down.md</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>You drive the target backward and finish the motion with a downward wrench that leaves them sprawled where they land.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>You back up three steps, lower your head, and throw yourself at them like a stone from a sling.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CHG-UNB-065</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crash-down</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>The Cannonball</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crash-down.md</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CHG-UNB-066</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crash-down</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>The Cannonball</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crash-down.md</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Brawn</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CHG-UNB-067</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crash-down</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>The Cannonball</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crash-down.md</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>One creature pushed by your Main Action attack or Force action.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>One creature within 4 squares.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CHG-UNB-068</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crash-down</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>The Cannonball</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crash-down.md</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>After that push resolves, you may knock the target prone even if it did not strike an obstruction. Then you may move 1 square toward it without provoking if a legal free square is available. This adds no collision damage and cannot create numbered Prone.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Move up to 4 squares in a straight line toward the target, ignoring difficult terrain. If you end adjacent to it, make a Brawn roll. Weak: 4 physical damage to the target. You take 3 physical damage and are Prone. Standard: 8 physical damage, and the target is Prone. You take 2 physical damage. Strong: 12 physical damage, and the target is Prone and Dazed 1. You take 1 physical damage and are Dazed 1. If you cannot move at least 2 squares, you cannot use this ability. Resolve collisions normally.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Hurler design.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CHG-UNB-069</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crash-down</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>The Cannonball</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crash-down.md</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Immediate knockdown and step.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Immediate; Prone and Dazed use their normal rules.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CHG-UNB-070</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crash-down</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>The Cannonball</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crash-down.md</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Skill / Control / Movement</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Control</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CHG-UNB-071</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CLS-09</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>signature-unbalanced-crash-down</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>The Cannonball</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>design/cards/signature-unbalanced-crash-down.md</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Once on your turn; no benefit from free attacks.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Once per scene.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q204"/>
